--- a/TIME TABLE SAMPLE DATA/INPUTS/UPDATED TIMETABLE TOTAL.xlsx
+++ b/TIME TABLE SAMPLE DATA/INPUTS/UPDATED TIMETABLE TOTAL.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{8B3F7FE1-F0AD-4AE2-A892-095831FE1093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1A23A6B-A519-49A1-AE67-5BFBFFB02B65}"/>
@@ -2724,6 +2724,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="U17:W17"/>
+    <mergeCell ref="U1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A17:A18"/>
@@ -2740,12 +2746,6 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="U17:W17"/>
-    <mergeCell ref="U1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
